--- a/Anexo1_base_errores.xlsx
+++ b/Anexo1_base_errores.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Registros con Errores" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Diccionario de Datos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Diccionario de Errores" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR79"/>
+  <dimension ref="A1:AD79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,97 +546,27 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>nombre_inversion</t>
+          <t>tipo_comentario</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>tipo_comentario</t>
+          <t>cod_local_dup</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>cod_local_dup</t>
+          <t>validacion_errores</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>err_cui</t>
+          <t>validacion_completo</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>err_tipo</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>err_monto</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>err_avance</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>err_f9</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>err_comp</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>err_unid</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>err_demol</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>err_nueva</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>err_reforz</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>err_cerco</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>err_sust</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>err_ampl</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>err_mobil</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>err_agua</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>err_elec</t>
+          <t>validacion_info</t>
         </is>
       </c>
     </row>
@@ -665,7 +596,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86278 MARIO TORRES MEZARINA</t>
+          <t>86278 MARIO TORRES MEZARINA/86278 MARIO TORRES MEZARINA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -763,61 +694,23 @@
           <t xml:space="preserve">CUI Nº2610327 QUE NO TIENEN NINGUN AVANCE FISICO (0%) </t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -845,7 +738,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>86278 MARIO TORRES MEZARINA</t>
+          <t>86278 MARIO TORRES MEZARINA/86278 MARIO TORRES MEZARINA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -943,61 +836,23 @@
           <t xml:space="preserve">CUI Nº2690883 QUE NO TIENEN NINGUN AVANCE FISICO (0%) </t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,7 +880,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>86278 MARIO TORRES MEZARINA</t>
+          <t>86278 MARIO TORRES MEZARINA/86278 MARIO TORRES MEZARINA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1123,61 +978,23 @@
           <t xml:space="preserve">CUI Nº2536436  TIENEN UN 100% DE EJECUCIÓN FISICA </t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1303,61 +1120,23 @@
           <t>CUI Nº2565542 TIENEN UN 100% DE EJECUCIÓN FISICA</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1385,7 +1164,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>86309 FLAVIO MAXIMO VEGA VILLANUEVA</t>
+          <t>86309 FLAVIO MAXIMO VEGA VILLANUEVA/86309 FLAVIO MAXIMO VEGA VILLANUEVA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1479,61 +1258,23 @@
           <t>EL PROYECTO CON CODIGO UNICO Nº2567347 RECIEN ESTA EN EXPEDIENTE TECNICO, POR LO QUE TODAVIA NO HAY NINGUNA EJECUCIÓN FISICA, PERO SE ESTIMA QUE SE CONSTRUYA UN NUEVO COLEGIO EN PAMPACANCHA Y MEJOREN SUS SERVICIOS EDUCATIVOS, POR LO TANTO A LAS PREGUNTAS QUE RESPONDI CON UN "NO" ES ACTUALMENTE LO QUE ESTA PASANDO, PERO PARA UN FUTURO SE ESPERA QUE SE CONSTRUYA UNA NUEVA INFRAESTRUCTURA DEL COLEGIO</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Error en: comp, unid</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1655,61 +1396,23 @@
           <t xml:space="preserve">EL PROYECTO CON CODIGO UNICO Nº2656983 RECIEN ESTA EN EXPEDIENTE TECNICO, POR LO QUE TODAVIA NO HAY NINGUNA EJECUCIÓN FISICA, PERO SE ESTIMA QUE SE CONSTRUYA UN NUEVO JARDIN EN ANTA, SE AMPLIEN Y MEJOREN SUS SERVICIOS EDUCATIVOS, POR LO TANTO A LAS PREGUNTAS QUE RESPONDI CON UN "NO" ES ACTUALMENTE LO QUE ESTA PASANDO, PERO PARA UN FUTURO SE ESPERA QUE SE CONSTRUYA UNA NUEVA INFRAESTRUCTURA DEL COLEGIO </t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Error en: comp, unid</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1831,61 +1534,23 @@
           <t>Se encuentra en proceso de elaboración del expediente técnico.</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2007,61 +1672,23 @@
           <t>Se encuentra en proceso de elaboración del expediente técnico.</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2183,61 +1810,23 @@
           <t>No se encuentra con ninguna intervención en la fase de ejecución.</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2265,7 +1854,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54181</t>
+          <t>54544</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2357,55 +1946,17 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2433,7 +1984,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54177 EL BUEN PASTOR</t>
+          <t>277-21 EL BUEN PASTOR/54177 EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2521,55 +2072,17 @@
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2685,55 +2198,17 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2761,7 +2236,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>54181</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2849,55 +2324,17 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3019,61 +2456,23 @@
           <t>Se realizo trabajos de mejoramiento en la institucion publica de la localidad de Cintiaro, priorizando trabajos para la adecuada educacion de los niños de educacion inicial.</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3195,61 +2594,23 @@
           <t>El proyecto 2590716, es un proyecto de innovacion pedagogica en la institucion.</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Error en: monto, comp</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3371,61 +2732,23 @@
           <t>El proyecto 2590716, es un proyecto de innovacion pedagogica en la institucion primaria.</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Error en: monto, comp</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3551,61 +2874,23 @@
           <t>SE CONSTRUYO 3 AULAS, UNA ESCALERA, UN SALA MULTIUSOS</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3633,7 +2918,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>429-158</t>
+          <t>38268/38268/38268</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3731,61 +3016,23 @@
           <t>Se realizo trabajos de mejoramiento en la institucion publica de la localidad de Vista Alegre, priorizando trabajos para la adecuada educacion de los niños de educacion inicial.</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3813,7 +3060,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>429-158</t>
+          <t>429-156</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3907,61 +3154,23 @@
           <t>Se realizo trabajos de mejoramiento en la institucion publica de la localidad de Sivia, priorizando trabajos para la adecuada educacion de los niños de educacion inicial.</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3989,7 +3198,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GUAYABO</t>
+          <t>82576</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4085,55 +3294,17 @@
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4161,7 +3332,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>82925</t>
+          <t>82925/82925</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4259,61 +3430,23 @@
           <t>Se realizo la ejecución de la I Etapa del proyecto</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4341,7 +3474,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>82926</t>
+          <t>82926/82926</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4433,55 +3566,17 @@
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4601,55 +3696,17 @@
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4775,61 +3832,23 @@
           <t>Se realizo la ejecución de la I Etapa del proyecto</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4953,55 +3972,17 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Error en: avance</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5123,61 +4104,23 @@
           <t>La intervención contempla los componentes de infraestructura, equipamiento y mobiliario educativo</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>EQUIPAMIENTO/MOBILIARIO</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5299,61 +4242,23 @@
           <t>La intervención contempla los componentes de infraestructura, equipamiento y mobiliario educativo</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>EQUIPAMIENTO/MOBILIARIO</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5381,7 +4286,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>51009 FRANCISCO SIVIRICHI</t>
+          <t>448 SANTA ANA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -5475,61 +4380,23 @@
           <t>La intervención contempla los componentes de infraestructura de proteccion solar (estructuras tensionarias), equipamiento y tratamietno de consumo de agua</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5557,7 +4424,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>51012 JULIO ALBERTO PONCE ANTUNEZ DE MAYOLO</t>
+          <t>51012 JULIO ALBERTO PONCE ANTUNEZ DE MAYOLO/51012 JULIO ALBERTO PONCE ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -5655,61 +4522,23 @@
           <t>La intervención contempla los componentes de infraestructura (solo sala de computo), equipamiento y mobiliario educativo</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>EQUIPAMIENTO/MOBILIARIO</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5831,61 +4660,23 @@
           <t>La intervención contempla los componentes de infraestructura, equipamiento y mobiliario educativo</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>EQUIPAMIENTO/MOBILIARIO</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5913,7 +4704,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>COMERCIO 41</t>
+          <t>COMERCIO 41/COMERCIO 41</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -6011,61 +4802,23 @@
           <t>La intervención contempla los componentes de equipamiento y mobiliario educativo</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>EQUIPAMIENTO/MOBILIARIO</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -6187,61 +4940,23 @@
           <t>La intervención contempla los componentes de infraestructura, equipamiento y mobiliario educativo</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>EQUIPAMIENTO/MOBILIARIO</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -6363,61 +5078,23 @@
           <t>ACTOS PREVIOS PARA LA ELABORACION DEL EXPEDIENTE TECNICO</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Error en: avance, comp, unid, demol, nueva, reforz, cerco, sust, ampl, mobil, agua, elec</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -6539,61 +5216,23 @@
           <t>EN ELABORACION DEL ELABORACION DEL EXPEDIENTE  PARA PRONIED</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Error en: avance, comp, unid, demol, nueva, reforz, cerco, sust, ampl, mobil, agua, elec</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -6621,7 +5260,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>56274</t>
+          <t>56274/56274/56274</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -6715,61 +5354,23 @@
           <t>EN ELABORACION DEL ELABORACION DEL EXPEDIENTE  PARA PRONIED</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Error en: avance, comp, unid, demol, nueva, reforz, cerco, sust, ampl, mobil, agua, elec</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -6891,61 +5492,23 @@
           <t>EN ELABORACION DEL ELABORACION DEL EXPEDIENTE  PARA PRONIED</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Error en: avance, comp, unid, demol, nueva, reforz, cerco, sust, ampl, mobil, agua, elec</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -7067,61 +5630,23 @@
           <t xml:space="preserve">PROYECTO CON EJECUCION FISICA AL 100% PENDIENTE DE LIQUIDACION </t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -7243,61 +5768,23 @@
           <t>PROYECTO QUE ESTA EN ETAPA DE ELABORACION DE EXPEDEINTE TECNCICO ACTUALMENTE SE CONCLUYO CON LA ETAPA DE REVISION TECNICA DEL EXPEDIENTE.</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -7419,61 +5906,23 @@
           <t>PROYECTO CON EXPEDIENTE TECNICO DESACTUALIZADO</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -7595,61 +6044,23 @@
           <t xml:space="preserve">PROYECTO EN EJECUCION FISICA ALA FECHA </t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>EN EJECUCION</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -7771,61 +6182,23 @@
           <t>PROYECTO SIN EJECUCION FISICA EN PROCESO DE ELABORACION DE EXPEDIENTE TECNICO</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>NO EJECUTADO</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -7947,61 +6320,23 @@
           <t xml:space="preserve">PROYECTO EN EJECUCIOPN FISICA </t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>EN EJECUCION</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -8123,61 +6458,23 @@
           <t>A LA FECHA SE CUENTA CON EXPEDEINTE TECNICO APROBADO SIN EMBARGO POR DISPONIBILIDAD PRESUPUESTAL NO SE INICIO CON LA EJECUCION FISICA</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>EN EJECUCION</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -8299,61 +6596,23 @@
           <t>OBRA CULMINADA AL 100 POR CIENTO CON UN AMBIENTE DE PREPARACION Y EXPENDIO DE ALIMENTOS</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Error en: monto, reforz</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -8475,61 +6734,23 @@
           <t>OBRA CONCLUIDA-COLOCACIÓN DE LA COBERTURA DE ALUZINC Y CANALETAS, EXCAVACIÓN PARA EL SISTEMA ELÉCTRICO Y POZA A TIERRA, CORTE DE PARED PARA LA INSTALACION</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -8557,7 +6778,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>51009 FRANCISCO SIVIRICHI</t>
+          <t>985</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8655,61 +6876,23 @@
           <t>La intervención contempla los componentes de infraestructura de proteccion solar (estructuras tensionarias), equipamiento y tratamietno de consumo de agua</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -8831,61 +7014,23 @@
           <t>el proyecto se encuentra  PI viable con programacion de se elaboracion del expediente tecnico</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -8913,7 +7058,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>50744</t>
+          <t>50744/50744/50744</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -9007,61 +7152,23 @@
           <t>el proyecto se encuentra  con expediente tecnico en evaluacion en PRONIED</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -9089,7 +7196,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>50913</t>
+          <t>50913/50913</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -9183,61 +7290,23 @@
           <t>el proyecto se encuentra  PI viable con programacion de se elaboracion del expediente tecnico</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -9361,55 +7430,17 @@
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -9535,61 +7566,23 @@
           <t>La intervencion que se realizo es con la realizacion de una losa deportiva.</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>INFRAESTRUCTURA DEPORTIVA</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -9711,61 +7704,23 @@
           <t>Actividades principales. Cubierta, Cielo Raso, Estudio Socio Ambiental seguridad y salud en el trabajo, obras provisionales, flete y movilizacion</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -9885,55 +7840,17 @@
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -10055,61 +7972,23 @@
           <t>EN EL BANCO DE INVERSIONES DE LA ENTIDAD, EL PIP SE ENCUENTRA VIABLE, PERO NO CUENTA CON EL RECURSO Y FINANCIAMIENTO PARA SU EJECUCION</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>SIN FINANCIAMIENTO</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Error en: unid, demol, nueva, reforz, cerco, sust, ampl, mobil, agua, elec</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -10137,7 +8016,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HORACIO ZEBALLOS GAMEZ</t>
+          <t>CARUMAS/HORACIO ZEBALLOS GAMEZ/HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -10231,61 +8110,23 @@
           <t>EN PROCESO DE LIQUIDACION</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>EN LIQUIDACION</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -10407,61 +8248,23 @@
           <t>FECHA DE CULMINACIÓN NOVIEMBRE DE 2020</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -10583,61 +8386,23 @@
           <t>TRANSFERIDA AL GORE MOQUEGUA EN 2024 , NO CULMINADA</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -10665,7 +8430,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>15016 SAGRADA FAMILIA</t>
+          <t>15016 SAGRADA FAMILIA/15016 SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -10755,61 +8520,23 @@
           <t>CULMINADA</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr"/>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Error en: nueva, cerco, ampl, mobil, agua, elec</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -10931,61 +8658,23 @@
           <t xml:space="preserve">UEI Municipalidad Provincial de Piura. </t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -11013,7 +8702,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LIBERTADORES DE AMERICA</t>
+          <t>LIBERTADORES DE AMERICA/LIBERTADORES DE AMERICA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -11107,61 +8796,23 @@
           <t>UEI Municipalidad Distrital de La Union // Cerrada</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -11283,61 +8934,23 @@
           <t xml:space="preserve">Obra Culminada // UEI Municipalidad Provincial de Piura. </t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -11459,61 +9072,23 @@
           <t>UEI Municipalidad Distrital de Tambo Grande</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -11631,61 +9206,23 @@
           <t xml:space="preserve">UEI Municipalidad Distrital de Tambo Grande, obra culminada, ejecutada por etapas, según ssi falta cancelar saldos a favor. </t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr"/>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -11713,7 +9250,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>AUGUSTO SALAZAR BONDY/AUGUSTO SALAZAR BONDY/AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -11807,61 +9344,23 @@
           <t>CULMINADA</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Error en: demol</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -11889,7 +9388,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>354</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -11983,61 +9482,23 @@
           <t>CULMINADA</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>OBRA CULMINADA</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -12159,61 +9620,23 @@
           <t xml:space="preserve">Este proyecto fue financiado a traves de PRONIED, el proyecto fue cerrado en el banco de inversiones </t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr"/>
-      <c r="AC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -12241,7 +9664,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>56039</t>
+          <t>56443/56039</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -12335,61 +9758,23 @@
           <t xml:space="preserve">Construccion y instalacion de cobertura techo metalico  de 788.43 m2, para loza de institucion educativa </t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr"/>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -12509,55 +9894,17 @@
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr"/>
-      <c r="AB69" t="inlineStr"/>
-      <c r="AC69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR69" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -12677,55 +10024,17 @@
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr"/>
-      <c r="AB70" t="inlineStr"/>
-      <c r="AC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR70" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -12845,55 +10154,17 @@
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr"/>
-      <c r="AB71" t="inlineStr"/>
-      <c r="AC71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR71" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -13013,55 +10284,17 @@
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
-      <c r="AB72" t="inlineStr"/>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR72" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -13181,55 +10414,17 @@
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
-      <c r="AB73" t="inlineStr"/>
-      <c r="AC73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR73" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -13351,61 +10546,23 @@
           <t>Inversión cerrada. IOARR cuenta con transferencia de Infraestructura a la entidad receptora U.E. N°301-0927 UGEL SAN MARTÍN mediante Resolución Gerencial Territorial N°061-2025-GRSM/GTBM-T con fecha 10 de marzo del 2025.</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr"/>
-      <c r="AC74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -13527,61 +10684,23 @@
           <t>SE ENCUENTRA EN ELABORACION DE EXPEDIENTE TECNICO</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>EXPEDIENTE TECNICO/PERFIL</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr"/>
-      <c r="AC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR75" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -13707,61 +10826,23 @@
           <t>INTERVENCION SOBRE VESTIDORES Y SSHH</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr"/>
-      <c r="AC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR76" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -13789,7 +10870,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>42262 JUVENAL UBALDO ORDOÑEZ SALAZAR</t>
+          <t>42262 JUVENAL UBALDO ORDOÑEZ SALAZAR/42262 JUVENAL UBALDO ORDOÑEZ SALAZAR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -13887,61 +10968,23 @@
           <t>LA INTERVENCION CORRESPONDE A LA INTERVENCIÓN DEL CAMPO DEPORTIVO</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>INFRAESTRUCTURA DEPORTIVA</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr"/>
-      <c r="AC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR77" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Error en: monto</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -13969,7 +11012,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>COAR UCAYALI</t>
+          <t>64035 AGROPECUARIO/COAR UCAYALI/64035 AGROPECUARIO/64035 AGROPECUARIO/64035 AGROPECUARIO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -14061,55 +11104,17 @@
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
-      <c r="AC78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR78" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Error en: avance</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -14137,7 +11142,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MICAELA BASTIDAS</t>
+          <t>64153</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -14227,61 +11232,23 @@
           <t>EL PROYECTO LO ELABORO LA MUNI DE IPARI</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>OTRO</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr"/>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Error en: comp</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14294,7 +11261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14645,6 +11612,176 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>validacion_errores</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Detalle de campos con error. Ej: 'Error en: comp, monto'. Vacio si no tiene errores</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>validacion_completo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>'Completo' si todos los campos requeridos estan llenos. Si no: 'Incompleto: campo1, campo2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>validacion_info</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Diferencias encontradas con las bases maestras (Vinculaciones y Base Inversiones). Muestra campo, fuente, valor original y valor corregido</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Significado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>&lt;&lt;ERROR&gt;&gt; en cui</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>El CUI tiene caracteres no numericos y no se pudo rescatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>&lt;&lt;ERROR&gt;&gt; en tipo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>El tipo de inversion no es PI, IOARR ni IRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>&lt;&lt;ERROR&gt;&gt; en monto</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>El monto no es un numero valido o es negativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>&lt;&lt;ERROR&gt;&gt; en avance</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>El avance no es un porcentaje valido entre 0 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>&lt;&lt;ERROR&gt;&gt; en f9</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>El campo F9 no es SI ni NO (puede ser corrimiento de columnas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>&lt;&lt;ERROR&gt;&gt; en comp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>El componente no se pudo clasificar en las 4 categorias validas</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>&lt;&lt;ERROR&gt;&gt; en unid</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>El campo unid no es SI ni NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>&lt;&lt;ERROR&gt;&gt; en cod_mod</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>El codigo modular tiene texto que no son codigos numericos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>&lt;&lt;ERROR&gt;&gt; en demol/nueva/reforz/cerco/sust/ampl/mobil/agua/elec</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Campos SI/NO con valores invalidos (guiones, letras, numeros raros)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Anexo1_base_errores.xlsx
+++ b/Anexo1_base_errores.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>020606</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -705,11 +705,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>SE INTERVENDRAN EN: COCINA</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -821,7 +817,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>020606</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -884,11 +880,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>INSTALACIONES DEPORTIVAS</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1000,7 +992,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>020606</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1063,11 +1055,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>LOSA DEPORTIVA</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1179,7 +1167,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>020606</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1242,11 +1230,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>LOSA DEPORTIVA</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1362,7 +1346,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20625</t>
+          <t>020625</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1425,11 +1409,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>-----------------------</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1608,11 +1588,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-----------------------</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1728,7 +1704,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>034335</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1859,7 +1835,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16015</t>
+          <t>016015</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1994,7 +1970,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24807</t>
+          <t>024807</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2236,11 +2212,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2419,11 +2391,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2539,7 +2507,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>021371</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2817,7 +2785,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>045230</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2992,7 +2960,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>47521</t>
+          <t>047521</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3119,7 +3087,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>47540</t>
+          <t>047540</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3290,7 +3258,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>47559</t>
+          <t>047559</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3417,7 +3385,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>47564</t>
+          <t>047564</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3544,7 +3512,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>47583</t>
+          <t>047583</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3715,7 +3683,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>047601</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3886,7 +3854,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>47615</t>
+          <t>047615</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4013,7 +3981,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>47658</t>
+          <t>047658</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4136,7 +4104,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>47663</t>
+          <t>047663</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4942,7 +4910,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>79814</t>
+          <t>079814</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5121,7 +5089,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>080011</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5300,7 +5268,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>89196</t>
+          <t>089196</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5365,7 +5333,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>89196</t>
+          <t>0089196</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -5910,7 +5878,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>438259</t>
+          <t>0438259</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -6089,7 +6057,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>438648</t>
+          <t>0438648</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -6443,7 +6411,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>391128</t>
+          <t>0391128</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -6622,7 +6590,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>390732</t>
+          <t>0390732</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -8094,11 +8062,7 @@
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9781,7 +9745,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>206086</t>
+          <t>0206086</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -10143,7 +10107,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>207449</t>
+          <t>0207449</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -10503,11 +10467,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -10686,11 +10646,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -10869,11 +10825,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -11052,11 +11004,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
+      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -11172,7 +11120,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>047045</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -13025,11 +12973,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
+      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>SI</t>
@@ -13208,11 +13152,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>SI</t>
@@ -13391,11 +13331,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>SI</t>
@@ -13988,7 +13924,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>52640</t>
+          <t>052640</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -14051,11 +13987,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>I.E.I. 475-5</t>
-        </is>
-      </c>
+      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>SI</t>
@@ -14230,11 +14162,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>ALFONSO RODRIGUEZ NAJARRO</t>
-        </is>
-      </c>
+      <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15045,11 +14973,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15220,11 +15144,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15395,11 +15315,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -15534,11 +15450,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15709,11 +15621,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15884,11 +15792,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>NO</t>
@@ -16063,11 +15967,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>SI</t>
@@ -16234,11 +16134,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>SI</t>
@@ -16405,11 +16301,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>SI</t>
@@ -16580,11 +16472,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>SI</t>
@@ -16751,11 +16639,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>SI</t>
@@ -16922,11 +16806,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>SI</t>
@@ -17093,11 +16973,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>SI</t>
@@ -17264,11 +17140,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>SI</t>
@@ -17435,11 +17307,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>SI</t>
@@ -17610,11 +17478,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>SI</t>
@@ -17785,11 +17649,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>SI</t>
@@ -17960,11 +17820,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>SI</t>
@@ -18135,11 +17991,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>SI</t>
@@ -18310,11 +18162,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>SI</t>
@@ -18485,11 +18333,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>SI</t>
@@ -18656,11 +18500,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>SI</t>
@@ -18827,11 +18667,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>SI</t>
@@ -18998,11 +18834,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>SI</t>
@@ -19169,11 +19001,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>SI</t>
@@ -19340,11 +19168,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>SI</t>
@@ -19511,11 +19335,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>SI</t>
@@ -19682,11 +19502,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>SI</t>
@@ -19853,11 +19669,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>SI</t>
@@ -20028,11 +19840,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>SI</t>
@@ -20203,11 +20011,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>SI</t>
@@ -20378,11 +20182,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>SI</t>
@@ -20553,11 +20353,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>SI</t>
@@ -20728,11 +20524,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>SI</t>
@@ -20903,11 +20695,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>SI</t>
@@ -21078,11 +20866,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>SI</t>
@@ -21253,11 +21037,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>SI</t>
@@ -21428,11 +21208,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>SI</t>
@@ -21607,11 +21383,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -26271,11 +26043,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -26450,11 +26218,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -26629,11 +26393,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -26808,11 +26568,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -26987,11 +26743,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -27166,11 +26918,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -27345,11 +27093,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -27524,11 +27268,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -27703,11 +27443,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -27882,11 +27618,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>NO</t>
@@ -28057,11 +27789,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -28232,11 +27960,7 @@
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>SI</t>
@@ -28407,11 +28131,7 @@
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>SI</t>
@@ -28578,11 +28298,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>NO</t>
@@ -28757,11 +28473,7 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -29117,7 +28829,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>321067</t>
+          <t>0321067</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">

--- a/Anexo1_base_errores.xlsx
+++ b/Anexo1_base_errores.xlsx
@@ -18633,7 +18633,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>253808</t>
+          <t>0253808</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">

--- a/Anexo1_base_errores.xlsx
+++ b/Anexo1_base_errores.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ177"/>
+  <dimension ref="A1:AW177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,6 +633,36 @@
           <t>cui_en_banco</t>
         </is>
       </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>cui_en_vinc</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>cod_local_oficial</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>cod_mod_oficial</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>cod_local_match</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>cod_mod_match</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>vinc_grupo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -812,6 +842,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -987,6 +1027,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -1055,7 +1105,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0906958</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1160,6 +1214,36 @@
       <c r="AQ4" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>020606</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0906958</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -1337,6 +1421,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1409,7 +1503,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0386144/1577576</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1514,6 +1612,36 @@
       <c r="AQ6" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>020625</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0386144/1577576</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -1695,6 +1823,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1826,6 +1964,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1890,7 +2038,11 @@
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0413419/0750034</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -1961,6 +2113,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>016015</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0413419/0750034</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2140,6 +2322,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2212,7 +2404,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0577684</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2317,6 +2513,36 @@
       <c r="AQ11" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>526757</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0577684</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -2498,6 +2724,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2566,7 +2802,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1355080/1554906</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -2637,6 +2877,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>021371/732762</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>1355080/1554906</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2705,7 +2975,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1355080/1554906</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -2776,6 +3050,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>021371/732762</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>1355080/1554906</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2848,7 +3152,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0283333/0283671/0508606</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2949,6 +3257,36 @@
       <c r="AQ15" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>045230/047583/047601</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0283333/0283671/0508606</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3349,11 @@
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0667436/1090257/1358498</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -3078,6 +3420,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>047521</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>0667436/1090257/1358498</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3146,7 +3518,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0283291/1330505</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>NO</t>
@@ -3247,6 +3623,36 @@
       <c r="AQ17" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>047540</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0283291/1330505</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3715,11 @@
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1392380</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -3376,6 +3786,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>047559</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>1392380</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3436,7 +3876,11 @@
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1384486</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -3503,6 +3947,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>047564</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>1384486</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Superior no universitaria</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3571,7 +4045,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0283333/0283671/0508606</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>NO</t>
@@ -3672,6 +4150,36 @@
       <c r="AQ20" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>045230/047583/047601</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>0283333/0283671/0508606</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -3742,7 +4250,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0283333/0283671/0508606</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>NO</t>
@@ -3843,6 +4355,36 @@
       <c r="AQ21" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>045230/047583/047601</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>0283333/0283671/0508606</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -3905,7 +4447,11 @@
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0283689</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -3972,6 +4518,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>047615</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>0283689</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4028,7 +4604,11 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0283739</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -4093,6 +4673,36 @@
       <c r="AQ23" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>047658</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>0283739</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -4218,6 +4828,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4278,7 +4898,11 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1330893</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -4343,6 +4967,36 @@
       <c r="AQ25" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>258655</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>1330893</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -4472,6 +5126,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4528,7 +5192,11 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1259001</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -4595,6 +5263,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>543549</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>1259001</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4655,7 +5353,11 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1585140</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -4722,6 +5424,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>655730</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>1585140</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4794,7 +5526,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1650589/1650654/1651082</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>NO</t>
@@ -4899,6 +5635,36 @@
       <c r="AQ29" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>561152/733158/733399</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>1650589/1650654/1651082</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -5080,6 +5846,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5259,6 +6035,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5442,6 +6228,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5625,6 +6421,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>561152/733158/733399</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>1650589/1650654/1651082</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5697,7 +6523,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1650589/1650654/1651082</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>NO</t>
@@ -5802,6 +6632,36 @@
       <c r="AQ34" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>561152/733158/733399</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>1650589/1650654/1651082</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -5983,6 +6843,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>3988107</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6166,6 +7056,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6341,6 +7241,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6516,6 +7426,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>110635</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>0391128</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6699,6 +7639,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>541178</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>0390732</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6763,7 +7733,11 @@
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0209049</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>SI</t>
@@ -6838,6 +7812,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>139403</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>0209049</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6902,7 +7906,11 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0207852/1083898</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>SI</t>
@@ -6977,6 +7985,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>139827</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>0207852/1083898</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7041,7 +8079,11 @@
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0656801</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>SI</t>
@@ -7116,6 +8158,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>140388</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>0656801</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7180,7 +8252,11 @@
       </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1396423</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>SI</t>
@@ -7255,6 +8331,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>553171</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>1396423</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7315,7 +8421,11 @@
       </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0209056</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>SI</t>
@@ -7390,6 +8500,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>143688</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>0209056</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7569,6 +8709,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>787349</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>1704758</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7633,7 +8803,11 @@
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0208975</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>SI</t>
@@ -7712,6 +8886,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>144305</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>0208975</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7776,7 +8980,11 @@
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0780676</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>SI</t>
@@ -7855,6 +9063,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>144503</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>0780676</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7919,7 +9157,11 @@
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0208652/0583104</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>SI</t>
@@ -7998,6 +9240,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>144536</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr">
+        <is>
+          <t>0208652/0583104</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8062,7 +9334,11 @@
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1238229</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8141,6 +9417,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>144777</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>1238229</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8205,7 +9511,11 @@
       </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1451236</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>SI</t>
@@ -8284,6 +9594,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>584894</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>1451236</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8348,7 +9688,11 @@
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1380690</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>SI</t>
@@ -8427,6 +9771,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>593638</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>1380690</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8487,7 +9861,11 @@
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1381367</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>SI</t>
@@ -8566,6 +9944,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>859510</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>1381367</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8630,7 +10038,11 @@
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1264431</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8709,6 +10121,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>595091</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>1264431</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8773,7 +10215,11 @@
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1744333</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>SI</t>
@@ -8848,6 +10294,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>819425</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
+          <t>1744333</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8912,7 +10388,11 @@
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1425966</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8991,6 +10471,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>820909</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr">
+        <is>
+          <t>1425966</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9055,7 +10565,11 @@
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1268846</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9134,6 +10648,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>852434</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>1268846</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9206,7 +10750,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1379544</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9311,6 +10859,36 @@
       <c r="AQ57" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>672305</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>1379544</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -9385,7 +10963,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0671800</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9490,6 +11072,36 @@
       <c r="AQ58" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>145965</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
+          <t>0671800</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -9564,7 +11176,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0206037/0206086/0206201/0207449/0233056/0233130/0236018/0236174/0236232/0236349/0236786/0403626/0403923/0403956/0403964/0403980/0404889/0472670/0486597/0489096/0517698/0520650/0520759/0522649/0565358/0565390/0591131/0591164/0591818/0621300/0627786/0671800/0671826/0671834/0730481/0730911/0731000/0731075/0731158/0731174/0731216/0734996/0735043/0772756/0782664/0785014/0785030/0785097/0927384/0927814/0928200/1060961/1061449/1061761/1322593/1336072/1349802/1370360/1370378/1386127/1386168/1386226/1386234/1522721/1615368/1615376</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>NO</t>
@@ -9669,6 +11285,36 @@
       <c r="AQ59" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>145927/145932/145965/145989/146007/146012/146031/146045/146069/146106/146125/146130/146154/146173/146187/146205/146253/146333/146366/146371/146432/147441/147554/147587/147592/147605/147610/147634/147653/147686/147827/148332/148346/148365/148431/148445/148577/148582/148600/148624/148638/148841/148855/148860/148879/148884/148898/148921/148935/148940/148964/148978/148983/149001/149015/149039/149058/149063/149077/149261/508447/518130/680598/680602/815149</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr">
+        <is>
+          <t>0206037/0206086/0206201/0207449/0233056/0233130/0236018/0236174/0236232/0236349/0236786/0403626/0403923/0403956/0403964/0403980/0404889/0472670/0486597/0489096/0517698/0520650/0520759/0522649/0565358/0565390/0591131/0591164/0591818/0621300/0627786/0671800/0671826/0671834/0730481/0730911/0731000/0731075/0731158/0731174/0731216/0734996/0735043/0772756/0782664/0785014/0785030/0785097/0927384/0927814/0928200/1060961/1061449/1061761/1322593/1336072/1349802/1370360/1370378/1386127/1386168/1386226/1386234/1522721/1615368/1615376</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -9854,6 +11500,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>146371</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>0206086</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9926,7 +11602,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0647230</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10031,6 +11711,36 @@
       <c r="AQ61" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>146413</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr">
+        <is>
+          <t>0647230</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -10216,6 +11926,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10288,7 +12008,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1643949</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10393,6 +12117,36 @@
       <c r="AQ63" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>727181</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr">
+        <is>
+          <t>1643949</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -10574,6 +12328,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10646,7 +12410,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0233908</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -10751,6 +12519,36 @@
       <c r="AQ65" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>158477</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr">
+        <is>
+          <t>0233908</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -10825,7 +12623,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0233924/1540988</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -10930,6 +12732,36 @@
       <c r="AQ66" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>158496</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr">
+        <is>
+          <t>0233924/1540988</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -11004,7 +12836,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1659044</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -11109,6 +12945,36 @@
       <c r="AQ67" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>741484</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr">
+        <is>
+          <t>1659044</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -11183,7 +13049,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0409946</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>SI</t>
@@ -11288,6 +13158,36 @@
       <c r="AQ68" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>047045</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
+          <t>0409946</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -11362,7 +13262,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0409581</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>SI</t>
@@ -11467,6 +13371,36 @@
       <c r="AQ69" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>169862</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr">
+        <is>
+          <t>0409581</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -11541,7 +13475,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0409607</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>SI</t>
@@ -11646,6 +13584,36 @@
       <c r="AQ70" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>169881</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>0409607</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -11720,7 +13688,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0409920</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>SI</t>
@@ -11825,6 +13797,36 @@
       <c r="AQ71" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>169937</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr">
+        <is>
+          <t>0409920</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -12006,6 +14008,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -12185,6 +14197,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -12360,6 +14382,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AU74" t="inlineStr"/>
+      <c r="AV74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -12432,7 +14464,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0488866</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>NO</t>
@@ -12537,6 +14573,36 @@
       <c r="AQ75" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>170059</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr">
+        <is>
+          <t>0488866</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -12611,7 +14677,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0933788</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>NO</t>
@@ -12716,6 +14786,36 @@
       <c r="AQ76" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>170083</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>0933788</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Superior no universitaria</t>
         </is>
       </c>
     </row>
@@ -12901,6 +15001,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>145927/145932/145965/145989/146007/146012/146031/146045/146069/146106/146125/146130/146154/146173/146187/146205/146253/146333/146366/146371/146432/147441/147554/147587/147592/147605/147610/147634/147653/147686/147827/148332/148346/148365/148431/148445/148577/148582/148600/148624/148638/148841/148855/148860/148879/148884/148898/148921/148935/148940/148964/148978/148983/149001/149015/149039/149058/149063/149077/149261/508447/518130/680598/680602/815149</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>0206037/0206086/0206201/0207449/0233056/0233130/0236018/0236174/0236232/0236349/0236786/0403626/0403923/0403956/0403964/0403980/0404889/0472670/0486597/0489096/0517698/0520650/0520759/0522649/0565358/0565390/0591131/0591164/0591818/0621300/0627786/0671800/0671826/0671834/0730481/0730911/0731000/0731075/0731158/0731174/0731216/0734996/0735043/0772756/0782664/0785014/0785030/0785097/0927384/0927814/0928200/1060961/1061449/1061761/1322593/1336072/1349802/1370360/1370378/1386127/1386168/1386226/1386234/1522721/1615368/1615376</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -13080,6 +15210,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AU78" t="inlineStr"/>
+      <c r="AV78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -13152,7 +15292,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0205187/0783084/1437748</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>SI</t>
@@ -13257,6 +15401,36 @@
       <c r="AQ79" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>164157</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr">
+        <is>
+          <t>0205187/0783084/1437748</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -13438,6 +15612,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -13498,7 +15682,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1608827/1608850/1690551</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>SI</t>
@@ -13595,6 +15783,36 @@
       <c r="AQ81" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>672367/672391/774629</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr">
+        <is>
+          <t>1608827/1608850/1690551</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -13657,7 +15875,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1608827/1608850/1690551</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>SI</t>
@@ -13754,6 +15976,36 @@
       <c r="AQ82" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>672367/672391/774629</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr">
+        <is>
+          <t>1608827/1608850/1690551</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -13816,7 +16068,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1608827/1608850/1690551</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>SI</t>
@@ -13913,6 +16169,36 @@
       <c r="AQ83" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>672367/672391/774629</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr">
+        <is>
+          <t>1608827/1608850/1690551</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -13987,7 +16273,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1089101</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>SI</t>
@@ -14088,6 +16378,36 @@
       <c r="AQ84" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>052640</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr">
+        <is>
+          <t>1089101</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -14269,6 +16589,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AU85" t="inlineStr"/>
+      <c r="AV85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14329,7 +16659,11 @@
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0932657</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -14400,6 +16734,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>164567</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr">
+        <is>
+          <t>0932657</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -14468,7 +16832,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0935882</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>SI</t>
@@ -14569,6 +16937,36 @@
       <c r="AQ87" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>164874</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr">
+        <is>
+          <t>0935882</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -14734,6 +17132,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AU88" t="inlineStr"/>
+      <c r="AV88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -14806,7 +17214,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0932749/1395896</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>SI</t>
@@ -14903,6 +17315,36 @@
       <c r="AQ89" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>608908/608932</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr">
+        <is>
+          <t>0932749/1395896</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -14973,7 +17415,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0736678</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15074,6 +17520,36 @@
       <c r="AQ90" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>228296</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr">
+        <is>
+          <t>0736678</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -15144,7 +17620,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0861112</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15245,6 +17725,36 @@
       <c r="AQ91" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>228324</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr">
+        <is>
+          <t>0861112</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -15382,6 +17892,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AU92" t="inlineStr"/>
+      <c r="AV92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15450,7 +17970,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0380295</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15551,6 +18075,36 @@
       <c r="AQ93" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>228376</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
+          <t>0380295</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -15621,7 +18175,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0609412</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15722,6 +18280,36 @@
       <c r="AQ94" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>228395</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr">
+        <is>
+          <t>0609412</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -15792,7 +18380,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0373035</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>NO</t>
@@ -15897,6 +18489,36 @@
       <c r="AQ95" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>228418</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr">
+        <is>
+          <t>0373035</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -15967,7 +18589,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1169820</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>SI</t>
@@ -16066,6 +18692,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>253120</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr">
+        <is>
+          <t>1169820</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -16233,6 +18889,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AU97" t="inlineStr"/>
+      <c r="AV97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -16301,7 +18967,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0366849</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>SI</t>
@@ -16400,6 +19070,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>253177</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr">
+        <is>
+          <t>0366849</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -16472,7 +19172,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1169903/1370766/1389162</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>SI</t>
@@ -16571,6 +19275,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>659530</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr">
+        <is>
+          <t>1169903/1370766/1389162</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -16738,6 +19472,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AU100" t="inlineStr"/>
+      <c r="AV100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -16905,6 +19649,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AU101" t="inlineStr"/>
+      <c r="AV101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -16973,7 +19727,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>1170430</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>SI</t>
@@ -17072,6 +19830,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>253422</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr">
+        <is>
+          <t>1170430</t>
+        </is>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -17140,7 +19928,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0366096/0577825</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>SI</t>
@@ -17239,6 +20031,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>253479</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr">
+        <is>
+          <t>0366096/0577825</t>
+        </is>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -17406,6 +20228,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AU104" t="inlineStr"/>
+      <c r="AV104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -17577,6 +20409,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AU105" t="inlineStr"/>
+      <c r="AV105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -17748,6 +20590,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AU106" t="inlineStr"/>
+      <c r="AV106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -17820,7 +20672,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>1603158</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>SI</t>
@@ -17919,6 +20775,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>668619</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr">
+        <is>
+          <t>1603158</t>
+        </is>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -18090,6 +20976,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AU108" t="inlineStr"/>
+      <c r="AV108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -18261,6 +21157,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AU109" t="inlineStr"/>
+      <c r="AV109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -18333,7 +21239,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>1656016</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>SI</t>
@@ -18432,6 +21342,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>737552</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr">
+        <is>
+          <t>1656016</t>
+        </is>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -18599,6 +21539,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AU111" t="inlineStr"/>
+      <c r="AV111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -18766,6 +21716,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AU112" t="inlineStr"/>
+      <c r="AV112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -18933,6 +21893,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AU113" t="inlineStr"/>
+      <c r="AV113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -19100,6 +22070,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AU114" t="inlineStr"/>
+      <c r="AV114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -19267,6 +22247,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AU115" t="inlineStr"/>
+      <c r="AV115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -19335,7 +22325,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>0757740/1389154</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>SI</t>
@@ -19434,6 +22428,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>253894</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr">
+        <is>
+          <t>0757740/1389154</t>
+        </is>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -19502,7 +22526,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>1171271</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>SI</t>
@@ -19601,6 +22629,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>253907</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr">
+        <is>
+          <t>1171271</t>
+        </is>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -19768,6 +22826,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AU118" t="inlineStr"/>
+      <c r="AV118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -19840,7 +22908,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>0366039/0394478/0395079/1359595/1763887</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>SI</t>
@@ -19939,6 +23011,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>253993</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>0366039/0394478/0395079/1359595/1763887</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20011,7 +23113,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>0822296/1470434</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>SI</t>
@@ -20110,6 +23216,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>658615</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr">
+        <is>
+          <t>0822296/1470434</t>
+        </is>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20182,7 +23318,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>1603125</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>SI</t>
@@ -20281,6 +23421,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>679284</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr">
+        <is>
+          <t>1603125</t>
+        </is>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -20452,6 +23622,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AU122" t="inlineStr"/>
+      <c r="AV122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20623,6 +23803,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AU123" t="inlineStr"/>
+      <c r="AV123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20695,7 +23885,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>1656032</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>SI</t>
@@ -20794,6 +23988,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>737571</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr">
+        <is>
+          <t>1656032</t>
+        </is>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -20965,6 +24189,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AU125" t="inlineStr"/>
+      <c r="AV125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21136,6 +24370,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AU126" t="inlineStr"/>
+      <c r="AV126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -21208,7 +24452,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>0430835</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>SI</t>
@@ -21309,6 +24557,36 @@
       <c r="AQ127" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>515495</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr">
+        <is>
+          <t>0430835</t>
+        </is>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -21490,6 +24768,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AU128" t="inlineStr"/>
+      <c r="AV128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21562,7 +24850,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>0309872/0322099/0322107/0322123/0322131/0322149/0322313/0708735/0745778/0837328/1523596</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>NO</t>
@@ -21667,6 +24959,36 @@
       <c r="AQ129" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>397227/397232/397246/397251/397265/397289/397294/397326/614099</t>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr">
+        <is>
+          <t>0309872/0322099/0322107/0322123/0322131/0322149/0322313/0708735/0745778/0837328/1523596</t>
+        </is>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -21741,7 +25063,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>0322149/1126416</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>NO</t>
@@ -21846,6 +25172,36 @@
       <c r="AQ130" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>397166/397265</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr">
+        <is>
+          <t>0322149/1126416</t>
+        </is>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -22027,6 +25383,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AU131" t="inlineStr"/>
+      <c r="AV131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -22095,7 +25461,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>0343111</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>SI</t>
@@ -22200,6 +25570,36 @@
       <c r="AQ132" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>412505</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr">
+        <is>
+          <t>0343111</t>
+        </is>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -22274,7 +25674,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>1745777</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>SI</t>
@@ -22379,6 +25783,36 @@
       <c r="AQ133" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>821027</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr">
+        <is>
+          <t>1745777</t>
+        </is>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -22453,7 +25887,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>0343269/1016468</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>SI</t>
@@ -22558,6 +25996,36 @@
       <c r="AQ134" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>857568</t>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr">
+        <is>
+          <t>0343269/1016468</t>
+        </is>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -22624,7 +26092,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>1206630</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>SI</t>
@@ -22729,6 +26201,36 @@
       <c r="AQ135" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>829716</t>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr">
+        <is>
+          <t>1206630</t>
+        </is>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Superior no universitaria</t>
         </is>
       </c>
     </row>
@@ -22803,7 +26305,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>1745504</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>SI</t>
@@ -22908,6 +26414,36 @@
       <c r="AQ136" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>820589</t>
+        </is>
+      </c>
+      <c r="AT136" t="inlineStr">
+        <is>
+          <t>1745504</t>
+        </is>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -22982,7 +26518,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>1715499</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>SI</t>
@@ -23087,6 +26627,36 @@
       <c r="AQ137" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>796848</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr">
+        <is>
+          <t>1715499</t>
+        </is>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -23157,7 +26727,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>1715648</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>SI</t>
@@ -23262,6 +26836,36 @@
       <c r="AQ138" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>796990</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr">
+        <is>
+          <t>1715648</t>
+        </is>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -23336,7 +26940,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>1745728</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
@@ -23411,6 +27019,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>820971</t>
+        </is>
+      </c>
+      <c r="AT139" t="inlineStr">
+        <is>
+          <t>1745728</t>
+        </is>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -23475,7 +27113,11 @@
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>1745736</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
@@ -23546,6 +27188,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>820985</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr">
+        <is>
+          <t>1745736</t>
+        </is>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
@@ -23614,7 +27286,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>0537001</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -23719,6 +27395,36 @@
       <c r="AQ141" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>427875</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr">
+        <is>
+          <t>0537001</t>
+        </is>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -23789,7 +27495,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>0352930/0620815/1560820</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>SI</t>
@@ -23894,6 +27604,36 @@
       <c r="AQ142" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>427620</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr">
+        <is>
+          <t>0352930/0620815/1560820</t>
+        </is>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -23968,7 +27708,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>0679845</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>SI</t>
@@ -24073,6 +27817,36 @@
       <c r="AQ143" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>156765</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr">
+        <is>
+          <t>0679845</t>
+        </is>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -24147,7 +27921,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>0201830</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>NO</t>
@@ -24252,6 +28030,36 @@
       <c r="AQ144" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>156812</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
+          <t>0201830</t>
+        </is>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -24310,7 +28118,11 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>0201848/1712819</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
@@ -24381,6 +28193,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>156826</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr">
+        <is>
+          <t>0201848/1712819</t>
+        </is>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -24433,7 +28275,11 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>0499368</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
@@ -24504,6 +28350,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>156893</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr">
+        <is>
+          <t>0499368</t>
+        </is>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -24556,7 +28432,11 @@
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>0207654</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
@@ -24625,6 +28505,36 @@
       <c r="AQ147" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>156906</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr">
+        <is>
+          <t>0207654</t>
+        </is>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Técnico productiva</t>
         </is>
       </c>
     </row>
@@ -24750,6 +28660,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AU148" t="inlineStr"/>
+      <c r="AV148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -24822,7 +28742,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>0570648</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>NO</t>
@@ -24923,6 +28847,36 @@
       <c r="AQ149" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>490409</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr">
+        <is>
+          <t>0570648</t>
+        </is>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -24997,7 +28951,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>1557974</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>NO</t>
@@ -25098,6 +29056,36 @@
       <c r="AQ150" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>635619</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr">
+        <is>
+          <t>1557974</t>
+        </is>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -25172,7 +29160,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>1685015</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>NO</t>
@@ -25273,6 +29265,36 @@
       <c r="AQ151" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>769500</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr">
+        <is>
+          <t>1685015</t>
+        </is>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -25347,7 +29369,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>1685049</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>NO</t>
@@ -25448,6 +29474,36 @@
       <c r="AQ152" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>769538</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr">
+        <is>
+          <t>1685049</t>
+        </is>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -25522,7 +29578,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>1718600</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>NO</t>
@@ -25623,6 +29683,36 @@
       <c r="AQ153" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>800893</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr">
+        <is>
+          <t>1718600</t>
+        </is>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -25800,6 +29890,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AU154" t="inlineStr"/>
+      <c r="AV154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -25868,7 +29968,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>1095801</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>SI</t>
@@ -25973,6 +30077,36 @@
       <c r="AQ155" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>483456</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr">
+        <is>
+          <t>1095801</t>
+        </is>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -26043,7 +30177,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>0603514/1586247</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -26148,6 +30286,36 @@
       <c r="AQ156" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>468875</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr">
+        <is>
+          <t>0603514/1586247</t>
+        </is>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -26218,7 +30386,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>0603514/1586247</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -26323,6 +30495,36 @@
       <c r="AQ157" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>468875</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr">
+        <is>
+          <t>0603514/1586247</t>
+        </is>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -26393,7 +30595,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>1557016</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -26498,6 +30704,36 @@
       <c r="AQ158" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>799328</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr">
+        <is>
+          <t>1557016</t>
+        </is>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -26568,7 +30804,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>0707414/1319714</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -26673,6 +30913,36 @@
       <c r="AQ159" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>469422</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr">
+        <is>
+          <t>0707414/1319714</t>
+        </is>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -26743,7 +31013,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>1557016</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -26848,6 +31122,36 @@
       <c r="AQ160" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>799328</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr">
+        <is>
+          <t>1557016</t>
+        </is>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -26918,7 +31222,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>0707513/1118694</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -27023,6 +31331,36 @@
       <c r="AQ161" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>469530</t>
+        </is>
+      </c>
+      <c r="AT161" t="inlineStr">
+        <is>
+          <t>0707513/1118694</t>
+        </is>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -27093,7 +31431,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>0632216</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -27198,6 +31540,36 @@
       <c r="AQ162" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>469752</t>
+        </is>
+      </c>
+      <c r="AT162" t="inlineStr">
+        <is>
+          <t>0632216</t>
+        </is>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -27268,7 +31640,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>1557016</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -27373,6 +31749,36 @@
       <c r="AQ163" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>799328</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr">
+        <is>
+          <t>1557016</t>
+        </is>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -27550,6 +31956,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AU164" t="inlineStr"/>
+      <c r="AV164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -27618,7 +32034,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>1734342</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>NO</t>
@@ -27719,6 +32139,36 @@
       <c r="AQ165" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>812155</t>
+        </is>
+      </c>
+      <c r="AT165" t="inlineStr">
+        <is>
+          <t>1734342</t>
+        </is>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -27789,7 +32239,11 @@
           <t>&lt;&lt;ERROR&gt;&gt;</t>
         </is>
       </c>
-      <c r="O166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>0297762/1120229</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>&lt;&lt;ERROR&gt;&gt;</t>
@@ -27894,6 +32348,36 @@
       <c r="AQ166" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>479572</t>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr">
+        <is>
+          <t>0297762/1120229</t>
+        </is>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -27960,7 +32444,11 @@
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>0565242</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>SI</t>
@@ -28061,6 +32549,36 @@
       <c r="AQ167" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>476229</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr">
+        <is>
+          <t>0565242</t>
+        </is>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -28131,7 +32649,11 @@
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>0565242</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>SI</t>
@@ -28232,6 +32754,36 @@
       <c r="AQ168" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>476229</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr">
+        <is>
+          <t>0565242</t>
+        </is>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -28298,7 +32850,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>0301572</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>NO</t>
@@ -28403,6 +32959,36 @@
       <c r="AQ169" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>479949</t>
+        </is>
+      </c>
+      <c r="AT169" t="inlineStr">
+        <is>
+          <t>0301572</t>
+        </is>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -28580,6 +33166,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AU170" t="inlineStr"/>
+      <c r="AV170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
@@ -28755,6 +33351,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AU171" t="inlineStr"/>
+      <c r="AV171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -28938,6 +33544,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>489081</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr">
+        <is>
+          <t>0321067</t>
+        </is>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -29119,6 +33755,36 @@
       <c r="AQ173" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>810335</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr">
+        <is>
+          <t>1597251</t>
+        </is>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>
@@ -29292,6 +33958,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AU174" t="inlineStr"/>
+      <c r="AV174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -29415,6 +34091,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AU175" t="inlineStr"/>
+      <c r="AV175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -29530,6 +34216,16 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr"/>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AU176" t="inlineStr"/>
+      <c r="AV176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -29598,7 +34294,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>0584243</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>NO</t>
@@ -29703,6 +34403,36 @@
       <c r="AQ177" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>497769</t>
+        </is>
+      </c>
+      <c r="AT177" t="inlineStr">
+        <is>
+          <t>0584243</t>
+        </is>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Básica</t>
         </is>
       </c>
     </row>

--- a/Anexo1_base_errores.xlsx
+++ b/Anexo1_base_errores.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW177"/>
+  <dimension ref="A1:AX177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,30 +635,35 @@
       </c>
       <c r="AR1" t="inlineStr">
         <is>
+          <t>cui_en_mef</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
           <t>cui_en_vinc</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>cod_local_oficial</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>cod_mod_oficial</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>cod_local_match</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>cod_mod_match</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>vinc_grupo</t>
         </is>
@@ -847,11 +852,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -1032,11 +1042,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -1218,30 +1233,35 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
           <t>020606</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>0906958</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -1426,11 +1446,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1616,30 +1641,35 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
           <t>020625</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>0386144/1577576</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -1828,11 +1858,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1969,11 +2004,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2115,30 +2155,35 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
           <t>016015</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>0413419/0750034</t>
         </is>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -2327,11 +2372,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2517,30 +2567,35 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
           <t>526757</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>0577684</t>
         </is>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -2729,11 +2784,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2879,30 +2939,35 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
           <t>021371/732762</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
+      <c r="AU13" t="inlineStr">
         <is>
           <t>1355080/1554906</t>
         </is>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -3052,30 +3117,35 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
           <t>021371/732762</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
+      <c r="AU14" t="inlineStr">
         <is>
           <t>1355080/1554906</t>
         </is>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -3261,30 +3331,35 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
           <t>045230/047583/047601</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr">
+      <c r="AU15" t="inlineStr">
         <is>
           <t>0283333/0283671/0508606</t>
         </is>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -3422,30 +3497,35 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
           <t>047521</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
+      <c r="AU16" t="inlineStr">
         <is>
           <t>0667436/1090257/1358498</t>
         </is>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -3627,30 +3707,35 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
           <t>047540</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
+      <c r="AU17" t="inlineStr">
         <is>
           <t>0283291/1330505</t>
         </is>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW17" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -3788,30 +3873,35 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
           <t>047559</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
+      <c r="AU18" t="inlineStr">
         <is>
           <t>1392380</t>
         </is>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW18" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -3949,30 +4039,35 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
           <t>047564</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr">
+      <c r="AU19" t="inlineStr">
         <is>
           <t>1384486</t>
         </is>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW19" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Superior no universitaria</t>
         </is>
@@ -4154,30 +4249,35 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
           <t>045230/047583/047601</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
+      <c r="AU20" t="inlineStr">
         <is>
           <t>0283333/0283671/0508606</t>
         </is>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW20" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -4359,30 +4459,35 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
           <t>045230/047583/047601</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr">
+      <c r="AU21" t="inlineStr">
         <is>
           <t>0283333/0283671/0508606</t>
         </is>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW21" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -4520,30 +4625,35 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
           <t>047615</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr">
+      <c r="AU22" t="inlineStr">
         <is>
           <t>0283689</t>
         </is>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW22" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -4677,30 +4787,35 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
           <t>047658</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
+      <c r="AU23" t="inlineStr">
         <is>
           <t>0283739</t>
         </is>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -4833,11 +4948,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AU24" t="inlineStr"/>
       <c r="AV24" t="inlineStr"/>
       <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4971,30 +5091,35 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
           <t>258655</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr">
+      <c r="AU25" t="inlineStr">
         <is>
           <t>1330893</t>
         </is>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW25" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -5131,11 +5256,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AU26" t="inlineStr"/>
       <c r="AV26" t="inlineStr"/>
       <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5265,30 +5395,35 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
           <t>543549</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
+      <c r="AU27" t="inlineStr">
         <is>
           <t>1259001</t>
         </is>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW27" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -5426,30 +5561,35 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
           <t>655730</t>
         </is>
       </c>
-      <c r="AT28" t="inlineStr">
+      <c r="AU28" t="inlineStr">
         <is>
           <t>1585140</t>
         </is>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW28" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -5639,30 +5779,35 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
           <t>561152/733158/733399</t>
         </is>
       </c>
-      <c r="AT29" t="inlineStr">
+      <c r="AU29" t="inlineStr">
         <is>
           <t>1650589/1650654/1651082</t>
         </is>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW29" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -5851,11 +5996,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AU30" t="inlineStr"/>
       <c r="AV30" t="inlineStr"/>
       <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6040,11 +6190,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AU31" t="inlineStr"/>
       <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6233,11 +6388,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AU32" t="inlineStr"/>
       <c r="AV32" t="inlineStr"/>
       <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6423,30 +6583,35 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
           <t>561152/733158/733399</t>
         </is>
       </c>
-      <c r="AT33" t="inlineStr">
+      <c r="AU33" t="inlineStr">
         <is>
           <t>1650589/1650654/1651082</t>
         </is>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -6636,30 +6801,35 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
           <t>561152/733158/733399</t>
         </is>
       </c>
-      <c r="AT34" t="inlineStr">
+      <c r="AU34" t="inlineStr">
         <is>
           <t>1650589/1650654/1651082</t>
         </is>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW34" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -6845,30 +7015,35 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="AT35" t="inlineStr">
+      <c r="AU35" t="inlineStr">
         <is>
           <t>3988107</t>
         </is>
       </c>
-      <c r="AU35" t="inlineStr">
+      <c r="AV35" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV35" t="inlineStr">
+      <c r="AW35" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AW35" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -7061,11 +7236,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AU36" t="inlineStr"/>
       <c r="AV36" t="inlineStr"/>
       <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7246,11 +7426,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AU37" t="inlineStr"/>
       <c r="AV37" t="inlineStr"/>
       <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7428,30 +7613,35 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
           <t>110635</t>
         </is>
       </c>
-      <c r="AT38" t="inlineStr">
+      <c r="AU38" t="inlineStr">
         <is>
           <t>0391128</t>
         </is>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -7641,30 +7831,35 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
           <t>541178</t>
         </is>
       </c>
-      <c r="AT39" t="inlineStr">
+      <c r="AU39" t="inlineStr">
         <is>
           <t>0390732</t>
         </is>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -7814,30 +8009,35 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
           <t>139403</t>
         </is>
       </c>
-      <c r="AT40" t="inlineStr">
+      <c r="AU40" t="inlineStr">
         <is>
           <t>0209049</t>
         </is>
       </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV40" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW40" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -7987,30 +8187,35 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
           <t>139827</t>
         </is>
       </c>
-      <c r="AT41" t="inlineStr">
+      <c r="AU41" t="inlineStr">
         <is>
           <t>0207852/1083898</t>
         </is>
       </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV41" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW41" t="inlineStr">
+      <c r="AX41" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -8160,30 +8365,35 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
           <t>140388</t>
         </is>
       </c>
-      <c r="AT42" t="inlineStr">
+      <c r="AU42" t="inlineStr">
         <is>
           <t>0656801</t>
         </is>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW42" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -8333,30 +8543,35 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
           <t>553171</t>
         </is>
       </c>
-      <c r="AT43" t="inlineStr">
+      <c r="AU43" t="inlineStr">
         <is>
           <t>1396423</t>
         </is>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW43" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -8502,30 +8717,35 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
           <t>143688</t>
         </is>
       </c>
-      <c r="AT44" t="inlineStr">
+      <c r="AU44" t="inlineStr">
         <is>
           <t>0209056</t>
         </is>
       </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV44" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW44" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -8711,30 +8931,35 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
           <t>787349</t>
         </is>
       </c>
-      <c r="AT45" t="inlineStr">
+      <c r="AU45" t="inlineStr">
         <is>
           <t>1704758</t>
         </is>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -8888,30 +9113,35 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
           <t>144305</t>
         </is>
       </c>
-      <c r="AT46" t="inlineStr">
+      <c r="AU46" t="inlineStr">
         <is>
           <t>0208975</t>
         </is>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW46" t="inlineStr">
+      <c r="AX46" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -9065,30 +9295,35 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
           <t>144503</t>
         </is>
       </c>
-      <c r="AT47" t="inlineStr">
+      <c r="AU47" t="inlineStr">
         <is>
           <t>0780676</t>
         </is>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW47" t="inlineStr">
+      <c r="AX47" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -9242,30 +9477,35 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr">
+        <is>
           <t>144536</t>
         </is>
       </c>
-      <c r="AT48" t="inlineStr">
+      <c r="AU48" t="inlineStr">
         <is>
           <t>0208652/0583104</t>
         </is>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW48" t="inlineStr">
+      <c r="AX48" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -9419,30 +9659,35 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
           <t>144777</t>
         </is>
       </c>
-      <c r="AT49" t="inlineStr">
+      <c r="AU49" t="inlineStr">
         <is>
           <t>1238229</t>
         </is>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW49" t="inlineStr">
+      <c r="AX49" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -9596,30 +9841,35 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
           <t>584894</t>
         </is>
       </c>
-      <c r="AT50" t="inlineStr">
+      <c r="AU50" t="inlineStr">
         <is>
           <t>1451236</t>
         </is>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW50" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -9773,30 +10023,35 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
           <t>593638</t>
         </is>
       </c>
-      <c r="AT51" t="inlineStr">
+      <c r="AU51" t="inlineStr">
         <is>
           <t>1380690</t>
         </is>
       </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV51" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW51" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -9946,30 +10201,35 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
           <t>859510</t>
         </is>
       </c>
-      <c r="AT52" t="inlineStr">
+      <c r="AU52" t="inlineStr">
         <is>
           <t>1381367</t>
         </is>
       </c>
-      <c r="AU52" t="inlineStr">
+      <c r="AV52" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV52" t="inlineStr">
+      <c r="AW52" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW52" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -10123,30 +10383,35 @@
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
           <t>595091</t>
         </is>
       </c>
-      <c r="AT53" t="inlineStr">
+      <c r="AU53" t="inlineStr">
         <is>
           <t>1264431</t>
         </is>
       </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV53" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW53" t="inlineStr">
+      <c r="AX53" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -10296,30 +10561,35 @@
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
           <t>819425</t>
         </is>
       </c>
-      <c r="AT54" t="inlineStr">
+      <c r="AU54" t="inlineStr">
         <is>
           <t>1744333</t>
         </is>
       </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV54" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW54" t="inlineStr">
+      <c r="AX54" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -10473,30 +10743,35 @@
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr">
+        <is>
           <t>820909</t>
         </is>
       </c>
-      <c r="AT55" t="inlineStr">
+      <c r="AU55" t="inlineStr">
         <is>
           <t>1425966</t>
         </is>
       </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV55" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW55" t="inlineStr">
+      <c r="AX55" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -10650,30 +10925,35 @@
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
           <t>852434</t>
         </is>
       </c>
-      <c r="AT56" t="inlineStr">
+      <c r="AU56" t="inlineStr">
         <is>
           <t>1268846</t>
         </is>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW56" t="inlineStr">
+      <c r="AX56" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -10863,30 +11143,35 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
           <t>672305</t>
         </is>
       </c>
-      <c r="AT57" t="inlineStr">
+      <c r="AU57" t="inlineStr">
         <is>
           <t>1379544</t>
         </is>
       </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW57" t="inlineStr">
+      <c r="AX57" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -11076,30 +11361,35 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
           <t>145965</t>
         </is>
       </c>
-      <c r="AT58" t="inlineStr">
+      <c r="AU58" t="inlineStr">
         <is>
           <t>0671800</t>
         </is>
       </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV58" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW58" t="inlineStr">
+      <c r="AX58" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -11289,30 +11579,35 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr">
+        <is>
           <t>145927/145932/145965/145989/146007/146012/146031/146045/146069/146106/146125/146130/146154/146173/146187/146205/146253/146333/146366/146371/146432/147441/147554/147587/147592/147605/147610/147634/147653/147686/147827/148332/148346/148365/148431/148445/148577/148582/148600/148624/148638/148841/148855/148860/148879/148884/148898/148921/148935/148940/148964/148978/148983/149001/149015/149039/149058/149063/149077/149261/508447/518130/680598/680602/815149</t>
         </is>
       </c>
-      <c r="AT59" t="inlineStr">
+      <c r="AU59" t="inlineStr">
         <is>
           <t>0206037/0206086/0206201/0207449/0233056/0233130/0236018/0236174/0236232/0236349/0236786/0403626/0403923/0403956/0403964/0403980/0404889/0472670/0486597/0489096/0517698/0520650/0520759/0522649/0565358/0565390/0591131/0591164/0591818/0621300/0627786/0671800/0671826/0671834/0730481/0730911/0731000/0731075/0731158/0731174/0731216/0734996/0735043/0772756/0782664/0785014/0785030/0785097/0927384/0927814/0928200/1060961/1061449/1061761/1322593/1336072/1349802/1370360/1370378/1386127/1386168/1386226/1386234/1522721/1615368/1615376</t>
         </is>
       </c>
-      <c r="AU59" t="inlineStr">
+      <c r="AV59" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV59" t="inlineStr">
+      <c r="AW59" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW59" t="inlineStr">
+      <c r="AX59" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -11502,30 +11797,35 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
           <t>146371</t>
         </is>
       </c>
-      <c r="AT60" t="inlineStr">
+      <c r="AU60" t="inlineStr">
         <is>
           <t>0206086</t>
         </is>
       </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -11715,30 +12015,35 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr">
+        <is>
           <t>146413</t>
         </is>
       </c>
-      <c r="AT61" t="inlineStr">
+      <c r="AU61" t="inlineStr">
         <is>
           <t>0647230</t>
         </is>
       </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV61" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW61" t="inlineStr">
+      <c r="AX61" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -11931,11 +12236,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS62" t="inlineStr"/>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12121,30 +12431,35 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr">
+        <is>
           <t>727181</t>
         </is>
       </c>
-      <c r="AT63" t="inlineStr">
+      <c r="AU63" t="inlineStr">
         <is>
           <t>1643949</t>
         </is>
       </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV63" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW63" t="inlineStr">
+      <c r="AX63" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -12333,11 +12648,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS64" t="inlineStr"/>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AU64" t="inlineStr"/>
       <c r="AV64" t="inlineStr"/>
       <c r="AW64" t="inlineStr"/>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -12523,30 +12843,35 @@
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr">
+        <is>
           <t>158477</t>
         </is>
       </c>
-      <c r="AT65" t="inlineStr">
+      <c r="AU65" t="inlineStr">
         <is>
           <t>0233908</t>
         </is>
       </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW65" t="inlineStr">
+      <c r="AX65" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -12736,30 +13061,35 @@
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr">
+        <is>
           <t>158496</t>
         </is>
       </c>
-      <c r="AT66" t="inlineStr">
+      <c r="AU66" t="inlineStr">
         <is>
           <t>0233924/1540988</t>
         </is>
       </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV66" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW66" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -12949,30 +13279,35 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr">
+        <is>
           <t>741484</t>
         </is>
       </c>
-      <c r="AT67" t="inlineStr">
+      <c r="AU67" t="inlineStr">
         <is>
           <t>1659044</t>
         </is>
       </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV67" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW67" t="inlineStr">
+      <c r="AX67" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -13162,30 +13497,35 @@
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
           <t>047045</t>
         </is>
       </c>
-      <c r="AT68" t="inlineStr">
+      <c r="AU68" t="inlineStr">
         <is>
           <t>0409946</t>
         </is>
       </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV68" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW68" t="inlineStr">
+      <c r="AX68" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -13375,30 +13715,35 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr">
+        <is>
           <t>169862</t>
         </is>
       </c>
-      <c r="AT69" t="inlineStr">
+      <c r="AU69" t="inlineStr">
         <is>
           <t>0409581</t>
         </is>
       </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV69" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW69" t="inlineStr">
+      <c r="AX69" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -13588,30 +13933,35 @@
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
           <t>169881</t>
         </is>
       </c>
-      <c r="AT70" t="inlineStr">
+      <c r="AU70" t="inlineStr">
         <is>
           <t>0409607</t>
         </is>
       </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW70" t="inlineStr">
+      <c r="AX70" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -13801,30 +14151,35 @@
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr">
+        <is>
           <t>169937</t>
         </is>
       </c>
-      <c r="AT71" t="inlineStr">
+      <c r="AU71" t="inlineStr">
         <is>
           <t>0409920</t>
         </is>
       </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV71" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW71" t="inlineStr">
+      <c r="AX71" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -14013,11 +14368,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS72" t="inlineStr"/>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AU72" t="inlineStr"/>
       <c r="AV72" t="inlineStr"/>
       <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -14202,11 +14562,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS73" t="inlineStr"/>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AU73" t="inlineStr"/>
       <c r="AV73" t="inlineStr"/>
       <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -14387,11 +14752,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS74" t="inlineStr"/>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AU74" t="inlineStr"/>
       <c r="AV74" t="inlineStr"/>
       <c r="AW74" t="inlineStr"/>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -14577,30 +14947,35 @@
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr">
+        <is>
           <t>170059</t>
         </is>
       </c>
-      <c r="AT75" t="inlineStr">
+      <c r="AU75" t="inlineStr">
         <is>
           <t>0488866</t>
         </is>
       </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV75" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW75" t="inlineStr">
+      <c r="AX75" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -14790,30 +15165,35 @@
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr">
+        <is>
           <t>170083</t>
         </is>
       </c>
-      <c r="AT76" t="inlineStr">
+      <c r="AU76" t="inlineStr">
         <is>
           <t>0933788</t>
         </is>
       </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV76" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW76" t="inlineStr">
+      <c r="AX76" t="inlineStr">
         <is>
           <t>Superior no universitaria</t>
         </is>
@@ -15003,30 +15383,35 @@
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr">
+        <is>
           <t>145927/145932/145965/145989/146007/146012/146031/146045/146069/146106/146125/146130/146154/146173/146187/146205/146253/146333/146366/146371/146432/147441/147554/147587/147592/147605/147610/147634/147653/147686/147827/148332/148346/148365/148431/148445/148577/148582/148600/148624/148638/148841/148855/148860/148879/148884/148898/148921/148935/148940/148964/148978/148983/149001/149015/149039/149058/149063/149077/149261/508447/518130/680598/680602/815149</t>
         </is>
       </c>
-      <c r="AT77" t="inlineStr">
+      <c r="AU77" t="inlineStr">
         <is>
           <t>0206037/0206086/0206201/0207449/0233056/0233130/0236018/0236174/0236232/0236349/0236786/0403626/0403923/0403956/0403964/0403980/0404889/0472670/0486597/0489096/0517698/0520650/0520759/0522649/0565358/0565390/0591131/0591164/0591818/0621300/0627786/0671800/0671826/0671834/0730481/0730911/0731000/0731075/0731158/0731174/0731216/0734996/0735043/0772756/0782664/0785014/0785030/0785097/0927384/0927814/0928200/1060961/1061449/1061761/1322593/1336072/1349802/1370360/1370378/1386127/1386168/1386226/1386234/1522721/1615368/1615376</t>
         </is>
       </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV77" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AW77" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -15215,11 +15600,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS78" t="inlineStr"/>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AU78" t="inlineStr"/>
       <c r="AV78" t="inlineStr"/>
       <c r="AW78" t="inlineStr"/>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -15405,30 +15795,35 @@
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr">
+        <is>
           <t>164157</t>
         </is>
       </c>
-      <c r="AT79" t="inlineStr">
+      <c r="AU79" t="inlineStr">
         <is>
           <t>0205187/0783084/1437748</t>
         </is>
       </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV79" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW79" t="inlineStr">
+      <c r="AX79" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -15617,11 +16012,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS80" t="inlineStr"/>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AU80" t="inlineStr"/>
       <c r="AV80" t="inlineStr"/>
       <c r="AW80" t="inlineStr"/>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -15787,30 +16187,35 @@
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr">
+        <is>
           <t>672367/672391/774629</t>
         </is>
       </c>
-      <c r="AT81" t="inlineStr">
+      <c r="AU81" t="inlineStr">
         <is>
           <t>1608827/1608850/1690551</t>
         </is>
       </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV81" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW81" t="inlineStr">
+      <c r="AX81" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -15980,30 +16385,35 @@
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr">
+        <is>
           <t>672367/672391/774629</t>
         </is>
       </c>
-      <c r="AT82" t="inlineStr">
+      <c r="AU82" t="inlineStr">
         <is>
           <t>1608827/1608850/1690551</t>
         </is>
       </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV82" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW82" t="inlineStr">
+      <c r="AX82" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -16173,30 +16583,35 @@
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr">
+        <is>
           <t>672367/672391/774629</t>
         </is>
       </c>
-      <c r="AT83" t="inlineStr">
+      <c r="AU83" t="inlineStr">
         <is>
           <t>1608827/1608850/1690551</t>
         </is>
       </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV83" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW83" t="inlineStr">
+      <c r="AX83" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -16382,30 +16797,35 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr">
+        <is>
           <t>052640</t>
         </is>
       </c>
-      <c r="AT84" t="inlineStr">
+      <c r="AU84" t="inlineStr">
         <is>
           <t>1089101</t>
         </is>
       </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV84" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW84" t="inlineStr">
+      <c r="AX84" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -16594,11 +17014,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS85" t="inlineStr"/>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AU85" t="inlineStr"/>
       <c r="AV85" t="inlineStr"/>
       <c r="AW85" t="inlineStr"/>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16736,30 +17161,35 @@
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr">
+        <is>
           <t>164567</t>
         </is>
       </c>
-      <c r="AT86" t="inlineStr">
+      <c r="AU86" t="inlineStr">
         <is>
           <t>0932657</t>
         </is>
       </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV86" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW86" t="inlineStr">
+      <c r="AX86" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -16941,30 +17371,35 @@
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr">
+        <is>
           <t>164874</t>
         </is>
       </c>
-      <c r="AT87" t="inlineStr">
+      <c r="AU87" t="inlineStr">
         <is>
           <t>0935882</t>
         </is>
       </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV87" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW87" t="inlineStr">
+      <c r="AX87" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -17137,11 +17572,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS88" t="inlineStr"/>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AU88" t="inlineStr"/>
       <c r="AV88" t="inlineStr"/>
       <c r="AW88" t="inlineStr"/>
+      <c r="AX88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -17319,30 +17759,35 @@
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr">
+        <is>
           <t>608908/608932</t>
         </is>
       </c>
-      <c r="AT89" t="inlineStr">
+      <c r="AU89" t="inlineStr">
         <is>
           <t>0932749/1395896</t>
         </is>
       </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV89" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW89" t="inlineStr">
+      <c r="AX89" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -17524,30 +17969,35 @@
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr">
+        <is>
           <t>228296</t>
         </is>
       </c>
-      <c r="AT90" t="inlineStr">
+      <c r="AU90" t="inlineStr">
         <is>
           <t>0736678</t>
         </is>
       </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV90" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW90" t="inlineStr">
+      <c r="AX90" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -17729,30 +18179,35 @@
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr">
+        <is>
           <t>228324</t>
         </is>
       </c>
-      <c r="AT91" t="inlineStr">
+      <c r="AU91" t="inlineStr">
         <is>
           <t>0861112</t>
         </is>
       </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV91" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW91" t="inlineStr">
+      <c r="AX91" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -17897,11 +18352,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS92" t="inlineStr"/>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AU92" t="inlineStr"/>
       <c r="AV92" t="inlineStr"/>
       <c r="AW92" t="inlineStr"/>
+      <c r="AX92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -18079,30 +18539,35 @@
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
           <t>228376</t>
         </is>
       </c>
-      <c r="AT93" t="inlineStr">
+      <c r="AU93" t="inlineStr">
         <is>
           <t>0380295</t>
         </is>
       </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV93" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW93" t="inlineStr">
+      <c r="AX93" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -18284,30 +18749,35 @@
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr">
+        <is>
           <t>228395</t>
         </is>
       </c>
-      <c r="AT94" t="inlineStr">
+      <c r="AU94" t="inlineStr">
         <is>
           <t>0609412</t>
         </is>
       </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV94" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW94" t="inlineStr">
+      <c r="AX94" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -18493,30 +18963,35 @@
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr">
+        <is>
           <t>228418</t>
         </is>
       </c>
-      <c r="AT95" t="inlineStr">
+      <c r="AU95" t="inlineStr">
         <is>
           <t>0373035</t>
         </is>
       </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV95" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW95" t="inlineStr">
+      <c r="AX95" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -18694,30 +19169,35 @@
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr">
+        <is>
           <t>253120</t>
         </is>
       </c>
-      <c r="AT96" t="inlineStr">
+      <c r="AU96" t="inlineStr">
         <is>
           <t>1169820</t>
         </is>
       </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV96" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW96" t="inlineStr">
+      <c r="AX96" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -18894,11 +19374,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS97" t="inlineStr"/>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AU97" t="inlineStr"/>
       <c r="AV97" t="inlineStr"/>
       <c r="AW97" t="inlineStr"/>
+      <c r="AX97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -19072,30 +19557,35 @@
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr">
+        <is>
           <t>253177</t>
         </is>
       </c>
-      <c r="AT98" t="inlineStr">
+      <c r="AU98" t="inlineStr">
         <is>
           <t>0366849</t>
         </is>
       </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV98" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW98" t="inlineStr">
+      <c r="AX98" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -19277,30 +19767,35 @@
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr">
+        <is>
           <t>659530</t>
         </is>
       </c>
-      <c r="AT99" t="inlineStr">
+      <c r="AU99" t="inlineStr">
         <is>
           <t>1169903/1370766/1389162</t>
         </is>
       </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV99" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW99" t="inlineStr">
+      <c r="AX99" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -19477,11 +19972,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS100" t="inlineStr"/>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AU100" t="inlineStr"/>
       <c r="AV100" t="inlineStr"/>
       <c r="AW100" t="inlineStr"/>
+      <c r="AX100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19654,11 +20154,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS101" t="inlineStr"/>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AU101" t="inlineStr"/>
       <c r="AV101" t="inlineStr"/>
       <c r="AW101" t="inlineStr"/>
+      <c r="AX101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19832,30 +20337,35 @@
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr">
+        <is>
           <t>253422</t>
         </is>
       </c>
-      <c r="AT102" t="inlineStr">
+      <c r="AU102" t="inlineStr">
         <is>
           <t>1170430</t>
         </is>
       </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV102" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW102" t="inlineStr">
+      <c r="AX102" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -20033,30 +20543,35 @@
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr">
+        <is>
           <t>253479</t>
         </is>
       </c>
-      <c r="AT103" t="inlineStr">
+      <c r="AU103" t="inlineStr">
         <is>
           <t>0366096/0577825</t>
         </is>
       </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV103" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW103" t="inlineStr">
+      <c r="AX103" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -20233,11 +20748,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS104" t="inlineStr"/>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AU104" t="inlineStr"/>
       <c r="AV104" t="inlineStr"/>
       <c r="AW104" t="inlineStr"/>
+      <c r="AX104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -20414,11 +20934,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS105" t="inlineStr"/>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AU105" t="inlineStr"/>
       <c r="AV105" t="inlineStr"/>
       <c r="AW105" t="inlineStr"/>
+      <c r="AX105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -20595,11 +21120,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS106" t="inlineStr"/>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AU106" t="inlineStr"/>
       <c r="AV106" t="inlineStr"/>
       <c r="AW106" t="inlineStr"/>
+      <c r="AX106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -20777,30 +21307,35 @@
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr">
+        <is>
           <t>668619</t>
         </is>
       </c>
-      <c r="AT107" t="inlineStr">
+      <c r="AU107" t="inlineStr">
         <is>
           <t>1603158</t>
         </is>
       </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV107" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW107" t="inlineStr">
+      <c r="AX107" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -20981,11 +21516,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS108" t="inlineStr"/>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AU108" t="inlineStr"/>
       <c r="AV108" t="inlineStr"/>
       <c r="AW108" t="inlineStr"/>
+      <c r="AX108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -21162,11 +21702,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS109" t="inlineStr"/>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AU109" t="inlineStr"/>
       <c r="AV109" t="inlineStr"/>
       <c r="AW109" t="inlineStr"/>
+      <c r="AX109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -21344,30 +21889,35 @@
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr">
+        <is>
           <t>737552</t>
         </is>
       </c>
-      <c r="AT110" t="inlineStr">
+      <c r="AU110" t="inlineStr">
         <is>
           <t>1656016</t>
         </is>
       </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV110" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW110" t="inlineStr">
+      <c r="AX110" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -21544,11 +22094,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS111" t="inlineStr"/>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AU111" t="inlineStr"/>
       <c r="AV111" t="inlineStr"/>
       <c r="AW111" t="inlineStr"/>
+      <c r="AX111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -21721,11 +22276,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS112" t="inlineStr"/>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AU112" t="inlineStr"/>
       <c r="AV112" t="inlineStr"/>
       <c r="AW112" t="inlineStr"/>
+      <c r="AX112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -21898,11 +22458,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS113" t="inlineStr"/>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AU113" t="inlineStr"/>
       <c r="AV113" t="inlineStr"/>
       <c r="AW113" t="inlineStr"/>
+      <c r="AX113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -22075,11 +22640,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS114" t="inlineStr"/>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AU114" t="inlineStr"/>
       <c r="AV114" t="inlineStr"/>
       <c r="AW114" t="inlineStr"/>
+      <c r="AX114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -22252,11 +22822,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS115" t="inlineStr"/>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AU115" t="inlineStr"/>
       <c r="AV115" t="inlineStr"/>
       <c r="AW115" t="inlineStr"/>
+      <c r="AX115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -22430,30 +23005,35 @@
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr">
+        <is>
           <t>253894</t>
         </is>
       </c>
-      <c r="AT116" t="inlineStr">
+      <c r="AU116" t="inlineStr">
         <is>
           <t>0757740/1389154</t>
         </is>
       </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV116" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW116" t="inlineStr">
+      <c r="AX116" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -22631,30 +23211,35 @@
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr">
+        <is>
           <t>253907</t>
         </is>
       </c>
-      <c r="AT117" t="inlineStr">
+      <c r="AU117" t="inlineStr">
         <is>
           <t>1171271</t>
         </is>
       </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV117" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW117" t="inlineStr">
+      <c r="AX117" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -22831,11 +23416,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS118" t="inlineStr"/>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AU118" t="inlineStr"/>
       <c r="AV118" t="inlineStr"/>
       <c r="AW118" t="inlineStr"/>
+      <c r="AX118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -23013,30 +23603,35 @@
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
           <t>253993</t>
         </is>
       </c>
-      <c r="AT119" t="inlineStr">
+      <c r="AU119" t="inlineStr">
         <is>
           <t>0366039/0394478/0395079/1359595/1763887</t>
         </is>
       </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV119" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW119" t="inlineStr">
+      <c r="AX119" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -23218,30 +23813,35 @@
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr">
+        <is>
           <t>658615</t>
         </is>
       </c>
-      <c r="AT120" t="inlineStr">
+      <c r="AU120" t="inlineStr">
         <is>
           <t>0822296/1470434</t>
         </is>
       </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV120" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW120" t="inlineStr">
+      <c r="AX120" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -23423,30 +24023,35 @@
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr">
+        <is>
           <t>679284</t>
         </is>
       </c>
-      <c r="AT121" t="inlineStr">
+      <c r="AU121" t="inlineStr">
         <is>
           <t>1603125</t>
         </is>
       </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV121" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW121" t="inlineStr">
+      <c r="AX121" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -23627,11 +24232,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS122" t="inlineStr"/>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AU122" t="inlineStr"/>
       <c r="AV122" t="inlineStr"/>
       <c r="AW122" t="inlineStr"/>
+      <c r="AX122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -23808,11 +24418,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS123" t="inlineStr"/>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AU123" t="inlineStr"/>
       <c r="AV123" t="inlineStr"/>
       <c r="AW123" t="inlineStr"/>
+      <c r="AX123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -23990,30 +24605,35 @@
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr">
+        <is>
           <t>737571</t>
         </is>
       </c>
-      <c r="AT124" t="inlineStr">
+      <c r="AU124" t="inlineStr">
         <is>
           <t>1656032</t>
         </is>
       </c>
-      <c r="AU124" t="inlineStr">
+      <c r="AV124" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV124" t="inlineStr">
+      <c r="AW124" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW124" t="inlineStr">
+      <c r="AX124" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -24194,11 +24814,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS125" t="inlineStr"/>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AU125" t="inlineStr"/>
       <c r="AV125" t="inlineStr"/>
       <c r="AW125" t="inlineStr"/>
+      <c r="AX125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -24375,11 +25000,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS126" t="inlineStr"/>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AU126" t="inlineStr"/>
       <c r="AV126" t="inlineStr"/>
       <c r="AW126" t="inlineStr"/>
+      <c r="AX126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -24561,30 +25191,35 @@
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr">
+        <is>
           <t>515495</t>
         </is>
       </c>
-      <c r="AT127" t="inlineStr">
+      <c r="AU127" t="inlineStr">
         <is>
           <t>0430835</t>
         </is>
       </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV127" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW127" t="inlineStr">
+      <c r="AX127" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -24773,11 +25408,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS128" t="inlineStr"/>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AU128" t="inlineStr"/>
       <c r="AV128" t="inlineStr"/>
       <c r="AW128" t="inlineStr"/>
+      <c r="AX128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -24963,30 +25603,35 @@
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr">
+        <is>
           <t>397227/397232/397246/397251/397265/397289/397294/397326/614099</t>
         </is>
       </c>
-      <c r="AT129" t="inlineStr">
+      <c r="AU129" t="inlineStr">
         <is>
           <t>0309872/0322099/0322107/0322123/0322131/0322149/0322313/0708735/0745778/0837328/1523596</t>
         </is>
       </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV129" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW129" t="inlineStr">
+      <c r="AX129" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -25176,30 +25821,35 @@
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr">
+        <is>
           <t>397166/397265</t>
         </is>
       </c>
-      <c r="AT130" t="inlineStr">
+      <c r="AU130" t="inlineStr">
         <is>
           <t>0322149/1126416</t>
         </is>
       </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV130" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW130" t="inlineStr">
+      <c r="AX130" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -25388,11 +26038,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS131" t="inlineStr"/>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AU131" t="inlineStr"/>
       <c r="AV131" t="inlineStr"/>
       <c r="AW131" t="inlineStr"/>
+      <c r="AX131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -25574,30 +26229,35 @@
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr">
+        <is>
           <t>412505</t>
         </is>
       </c>
-      <c r="AT132" t="inlineStr">
+      <c r="AU132" t="inlineStr">
         <is>
           <t>0343111</t>
         </is>
       </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV132" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW132" t="inlineStr">
+      <c r="AX132" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -25787,30 +26447,35 @@
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr">
+        <is>
           <t>821027</t>
         </is>
       </c>
-      <c r="AT133" t="inlineStr">
+      <c r="AU133" t="inlineStr">
         <is>
           <t>1745777</t>
         </is>
       </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV133" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW133" t="inlineStr">
+      <c r="AX133" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -26000,30 +26665,35 @@
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr">
+        <is>
           <t>857568</t>
         </is>
       </c>
-      <c r="AT134" t="inlineStr">
+      <c r="AU134" t="inlineStr">
         <is>
           <t>0343269/1016468</t>
         </is>
       </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV134" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW134" t="inlineStr">
+      <c r="AX134" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -26205,30 +26875,35 @@
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr">
+        <is>
           <t>829716</t>
         </is>
       </c>
-      <c r="AT135" t="inlineStr">
+      <c r="AU135" t="inlineStr">
         <is>
           <t>1206630</t>
         </is>
       </c>
-      <c r="AU135" t="inlineStr">
+      <c r="AV135" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV135" t="inlineStr">
+      <c r="AW135" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW135" t="inlineStr">
+      <c r="AX135" t="inlineStr">
         <is>
           <t>Superior no universitaria</t>
         </is>
@@ -26418,30 +27093,35 @@
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT136" t="inlineStr">
+        <is>
           <t>820589</t>
         </is>
       </c>
-      <c r="AT136" t="inlineStr">
+      <c r="AU136" t="inlineStr">
         <is>
           <t>1745504</t>
         </is>
       </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV136" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW136" t="inlineStr">
+      <c r="AX136" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -26631,30 +27311,35 @@
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr">
+        <is>
           <t>796848</t>
         </is>
       </c>
-      <c r="AT137" t="inlineStr">
+      <c r="AU137" t="inlineStr">
         <is>
           <t>1715499</t>
         </is>
       </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV137" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW137" t="inlineStr">
+      <c r="AX137" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -26840,30 +27525,35 @@
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr">
+        <is>
           <t>796990</t>
         </is>
       </c>
-      <c r="AT138" t="inlineStr">
+      <c r="AU138" t="inlineStr">
         <is>
           <t>1715648</t>
         </is>
       </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV138" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW138" t="inlineStr">
+      <c r="AX138" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -27021,30 +27711,35 @@
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT139" t="inlineStr">
+        <is>
           <t>820971</t>
         </is>
       </c>
-      <c r="AT139" t="inlineStr">
+      <c r="AU139" t="inlineStr">
         <is>
           <t>1745728</t>
         </is>
       </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV139" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW139" t="inlineStr">
+      <c r="AX139" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -27190,30 +27885,35 @@
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr">
+        <is>
           <t>820985</t>
         </is>
       </c>
-      <c r="AT140" t="inlineStr">
+      <c r="AU140" t="inlineStr">
         <is>
           <t>1745736</t>
         </is>
       </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV140" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW140" t="inlineStr">
+      <c r="AX140" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -27399,30 +28099,35 @@
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr">
+        <is>
           <t>427875</t>
         </is>
       </c>
-      <c r="AT141" t="inlineStr">
+      <c r="AU141" t="inlineStr">
         <is>
           <t>0537001</t>
         </is>
       </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV141" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW141" t="inlineStr">
+      <c r="AX141" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -27608,30 +28313,35 @@
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr">
+        <is>
           <t>427620</t>
         </is>
       </c>
-      <c r="AT142" t="inlineStr">
+      <c r="AU142" t="inlineStr">
         <is>
           <t>0352930/0620815/1560820</t>
         </is>
       </c>
-      <c r="AU142" t="inlineStr">
+      <c r="AV142" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV142" t="inlineStr">
+      <c r="AW142" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW142" t="inlineStr">
+      <c r="AX142" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -27821,30 +28531,35 @@
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr">
+        <is>
           <t>156765</t>
         </is>
       </c>
-      <c r="AT143" t="inlineStr">
+      <c r="AU143" t="inlineStr">
         <is>
           <t>0679845</t>
         </is>
       </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV143" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW143" t="inlineStr">
+      <c r="AX143" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -28034,30 +28749,35 @@
       </c>
       <c r="AR144" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
           <t>156812</t>
         </is>
       </c>
-      <c r="AT144" t="inlineStr">
+      <c r="AU144" t="inlineStr">
         <is>
           <t>0201830</t>
         </is>
       </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV144" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW144" t="inlineStr">
+      <c r="AX144" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -28195,30 +28915,35 @@
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr">
+        <is>
           <t>156826</t>
         </is>
       </c>
-      <c r="AT145" t="inlineStr">
+      <c r="AU145" t="inlineStr">
         <is>
           <t>0201848/1712819</t>
         </is>
       </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV145" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW145" t="inlineStr">
+      <c r="AX145" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -28352,30 +29077,35 @@
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr">
+        <is>
           <t>156893</t>
         </is>
       </c>
-      <c r="AT146" t="inlineStr">
+      <c r="AU146" t="inlineStr">
         <is>
           <t>0499368</t>
         </is>
       </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV146" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW146" t="inlineStr">
+      <c r="AX146" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -28509,30 +29239,35 @@
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr">
+        <is>
           <t>156906</t>
         </is>
       </c>
-      <c r="AT147" t="inlineStr">
+      <c r="AU147" t="inlineStr">
         <is>
           <t>0207654</t>
         </is>
       </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV147" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW147" t="inlineStr">
+      <c r="AX147" t="inlineStr">
         <is>
           <t>Técnico productiva</t>
         </is>
@@ -28665,11 +29400,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS148" t="inlineStr"/>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AU148" t="inlineStr"/>
       <c r="AV148" t="inlineStr"/>
       <c r="AW148" t="inlineStr"/>
+      <c r="AX148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -28851,30 +29591,35 @@
       </c>
       <c r="AR149" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr">
+        <is>
           <t>490409</t>
         </is>
       </c>
-      <c r="AT149" t="inlineStr">
+      <c r="AU149" t="inlineStr">
         <is>
           <t>0570648</t>
         </is>
       </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV149" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW149" t="inlineStr">
+      <c r="AX149" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -29060,30 +29805,35 @@
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr">
+        <is>
           <t>635619</t>
         </is>
       </c>
-      <c r="AT150" t="inlineStr">
+      <c r="AU150" t="inlineStr">
         <is>
           <t>1557974</t>
         </is>
       </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV150" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW150" t="inlineStr">
+      <c r="AX150" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -29269,30 +30019,35 @@
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr">
+        <is>
           <t>769500</t>
         </is>
       </c>
-      <c r="AT151" t="inlineStr">
+      <c r="AU151" t="inlineStr">
         <is>
           <t>1685015</t>
         </is>
       </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV151" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW151" t="inlineStr">
+      <c r="AX151" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -29478,30 +30233,35 @@
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr">
+        <is>
           <t>769538</t>
         </is>
       </c>
-      <c r="AT152" t="inlineStr">
+      <c r="AU152" t="inlineStr">
         <is>
           <t>1685049</t>
         </is>
       </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV152" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW152" t="inlineStr">
+      <c r="AX152" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -29687,30 +30447,35 @@
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr">
+        <is>
           <t>800893</t>
         </is>
       </c>
-      <c r="AT153" t="inlineStr">
+      <c r="AU153" t="inlineStr">
         <is>
           <t>1718600</t>
         </is>
       </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV153" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW153" t="inlineStr">
+      <c r="AX153" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -29895,11 +30660,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS154" t="inlineStr"/>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AU154" t="inlineStr"/>
       <c r="AV154" t="inlineStr"/>
       <c r="AW154" t="inlineStr"/>
+      <c r="AX154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -30081,30 +30851,35 @@
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr">
+        <is>
           <t>483456</t>
         </is>
       </c>
-      <c r="AT155" t="inlineStr">
+      <c r="AU155" t="inlineStr">
         <is>
           <t>1095801</t>
         </is>
       </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV155" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW155" t="inlineStr">
+      <c r="AX155" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -30290,30 +31065,35 @@
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr">
+        <is>
           <t>468875</t>
         </is>
       </c>
-      <c r="AT156" t="inlineStr">
+      <c r="AU156" t="inlineStr">
         <is>
           <t>0603514/1586247</t>
         </is>
       </c>
-      <c r="AU156" t="inlineStr">
+      <c r="AV156" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV156" t="inlineStr">
+      <c r="AW156" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW156" t="inlineStr">
+      <c r="AX156" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -30499,30 +31279,35 @@
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr">
+        <is>
           <t>468875</t>
         </is>
       </c>
-      <c r="AT157" t="inlineStr">
+      <c r="AU157" t="inlineStr">
         <is>
           <t>0603514/1586247</t>
         </is>
       </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV157" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW157" t="inlineStr">
+      <c r="AX157" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -30708,30 +31493,35 @@
       </c>
       <c r="AR158" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr">
+        <is>
           <t>799328</t>
         </is>
       </c>
-      <c r="AT158" t="inlineStr">
+      <c r="AU158" t="inlineStr">
         <is>
           <t>1557016</t>
         </is>
       </c>
-      <c r="AU158" t="inlineStr">
+      <c r="AV158" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV158" t="inlineStr">
+      <c r="AW158" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW158" t="inlineStr">
+      <c r="AX158" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -30917,30 +31707,35 @@
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr">
+        <is>
           <t>469422</t>
         </is>
       </c>
-      <c r="AT159" t="inlineStr">
+      <c r="AU159" t="inlineStr">
         <is>
           <t>0707414/1319714</t>
         </is>
       </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV159" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW159" t="inlineStr">
+      <c r="AX159" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -31126,30 +31921,35 @@
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr">
+        <is>
           <t>799328</t>
         </is>
       </c>
-      <c r="AT160" t="inlineStr">
+      <c r="AU160" t="inlineStr">
         <is>
           <t>1557016</t>
         </is>
       </c>
-      <c r="AU160" t="inlineStr">
+      <c r="AV160" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV160" t="inlineStr">
+      <c r="AW160" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW160" t="inlineStr">
+      <c r="AX160" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -31335,30 +32135,35 @@
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT161" t="inlineStr">
+        <is>
           <t>469530</t>
         </is>
       </c>
-      <c r="AT161" t="inlineStr">
+      <c r="AU161" t="inlineStr">
         <is>
           <t>0707513/1118694</t>
         </is>
       </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV161" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW161" t="inlineStr">
+      <c r="AX161" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -31544,30 +32349,35 @@
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT162" t="inlineStr">
+        <is>
           <t>469752</t>
         </is>
       </c>
-      <c r="AT162" t="inlineStr">
+      <c r="AU162" t="inlineStr">
         <is>
           <t>0632216</t>
         </is>
       </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV162" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW162" t="inlineStr">
+      <c r="AX162" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -31753,30 +32563,35 @@
       </c>
       <c r="AR163" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr">
+        <is>
           <t>799328</t>
         </is>
       </c>
-      <c r="AT163" t="inlineStr">
+      <c r="AU163" t="inlineStr">
         <is>
           <t>1557016</t>
         </is>
       </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV163" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW163" t="inlineStr">
+      <c r="AX163" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -31961,11 +32776,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS164" t="inlineStr"/>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AU164" t="inlineStr"/>
       <c r="AV164" t="inlineStr"/>
       <c r="AW164" t="inlineStr"/>
+      <c r="AX164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -32143,30 +32963,35 @@
       </c>
       <c r="AR165" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT165" t="inlineStr">
+        <is>
           <t>812155</t>
         </is>
       </c>
-      <c r="AT165" t="inlineStr">
+      <c r="AU165" t="inlineStr">
         <is>
           <t>1734342</t>
         </is>
       </c>
-      <c r="AU165" t="inlineStr">
+      <c r="AV165" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV165" t="inlineStr">
+      <c r="AW165" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW165" t="inlineStr">
+      <c r="AX165" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -32352,30 +33177,35 @@
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr">
+        <is>
           <t>479572</t>
         </is>
       </c>
-      <c r="AT166" t="inlineStr">
+      <c r="AU166" t="inlineStr">
         <is>
           <t>0297762/1120229</t>
         </is>
       </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV166" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW166" t="inlineStr">
+      <c r="AX166" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -32553,30 +33383,35 @@
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr">
+        <is>
           <t>476229</t>
         </is>
       </c>
-      <c r="AT167" t="inlineStr">
+      <c r="AU167" t="inlineStr">
         <is>
           <t>0565242</t>
         </is>
       </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV167" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW167" t="inlineStr">
+      <c r="AX167" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -32758,30 +33593,35 @@
       </c>
       <c r="AR168" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr">
+        <is>
           <t>476229</t>
         </is>
       </c>
-      <c r="AT168" t="inlineStr">
+      <c r="AU168" t="inlineStr">
         <is>
           <t>0565242</t>
         </is>
       </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV168" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW168" t="inlineStr">
+      <c r="AX168" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -32963,30 +33803,35 @@
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT169" t="inlineStr">
+        <is>
           <t>479949</t>
         </is>
       </c>
-      <c r="AT169" t="inlineStr">
+      <c r="AU169" t="inlineStr">
         <is>
           <t>0301572</t>
         </is>
       </c>
-      <c r="AU169" t="inlineStr">
+      <c r="AV169" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV169" t="inlineStr">
+      <c r="AW169" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW169" t="inlineStr">
+      <c r="AX169" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -33171,11 +34016,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS170" t="inlineStr"/>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AU170" t="inlineStr"/>
       <c r="AV170" t="inlineStr"/>
       <c r="AW170" t="inlineStr"/>
+      <c r="AX170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
@@ -33356,11 +34206,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS171" t="inlineStr"/>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AU171" t="inlineStr"/>
       <c r="AV171" t="inlineStr"/>
       <c r="AW171" t="inlineStr"/>
+      <c r="AX171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -33546,30 +34401,35 @@
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr">
+        <is>
           <t>489081</t>
         </is>
       </c>
-      <c r="AT172" t="inlineStr">
+      <c r="AU172" t="inlineStr">
         <is>
           <t>0321067</t>
         </is>
       </c>
-      <c r="AU172" t="inlineStr">
+      <c r="AV172" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV172" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AW172" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -33759,30 +34619,35 @@
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr">
+        <is>
           <t>810335</t>
         </is>
       </c>
-      <c r="AT173" t="inlineStr">
+      <c r="AU173" t="inlineStr">
         <is>
           <t>1597251</t>
         </is>
       </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="AV173" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
@@ -33963,11 +34828,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS174" t="inlineStr"/>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AU174" t="inlineStr"/>
       <c r="AV174" t="inlineStr"/>
       <c r="AW174" t="inlineStr"/>
+      <c r="AX174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -34096,11 +34966,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS175" t="inlineStr"/>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AU175" t="inlineStr"/>
       <c r="AV175" t="inlineStr"/>
       <c r="AW175" t="inlineStr"/>
+      <c r="AX175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -34221,11 +35096,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AS176" t="inlineStr"/>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AU176" t="inlineStr"/>
       <c r="AV176" t="inlineStr"/>
       <c r="AW176" t="inlineStr"/>
+      <c r="AX176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -34407,30 +35287,35 @@
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AT177" t="inlineStr">
+        <is>
           <t>497769</t>
         </is>
       </c>
-      <c r="AT177" t="inlineStr">
+      <c r="AU177" t="inlineStr">
         <is>
           <t>0584243</t>
         </is>
       </c>
-      <c r="AU177" t="inlineStr">
+      <c r="AV177" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="AV177" t="inlineStr">
+      <c r="AW177" t="inlineStr">
         <is>
           <t>COMPLETADO</t>
         </is>
       </c>
-      <c r="AW177" t="inlineStr">
+      <c r="AX177" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
